--- a/ExcelTemplate.xlsx
+++ b/ExcelTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\php\lampp-docker8\htdocs\semi3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A55715-CE5D-4BA7-8497-465E458AF308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E763A89B-56D2-475B-AC4A-08C876B5BC90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12180" yWindow="405" windowWidth="15015" windowHeight="14850" xr2:uid="{2B997C6D-AAF3-4717-B502-049FD728102C}"/>
+    <workbookView xWindow="2730" yWindow="630" windowWidth="15015" windowHeight="14850" xr2:uid="{2B997C6D-AAF3-4717-B502-049FD728102C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>見積書</t>
     <rPh sb="0" eb="2">
@@ -207,6 +207,10 @@
     <rPh sb="4" eb="6">
       <t>キンガク</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>s</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -374,50 +378,50 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -774,136 +778,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="I4" s="14" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="I4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="14"/>
+      <c r="J4" s="5"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="I5" s="14" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="I5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J5" s="14"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="G10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:12" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="1:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="9"/>
+      <c r="I14" s="19"/>
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
@@ -912,299 +916,345 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
     <row r="16" spans="1:12" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
     </row>
     <row r="17" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
     </row>
     <row r="18" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
     </row>
     <row r="19" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
     <row r="20" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
     <row r="21" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
     <row r="22" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
     <row r="23" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
     <row r="24" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
     <row r="27" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
     <row r="28" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
     <row r="29" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="6"/>
-      <c r="I29" s="6"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
     <row r="30" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
     </row>
     <row r="31" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="17"/>
+      <c r="C31" s="10"/>
       <c r="D31" s="3" t="s">
         <v>4</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
     </row>
     <row r="32" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C32" s="18"/>
+      <c r="C32" s="11"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" spans="2:11" ht="20.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="18"/>
+      <c r="C33" s="11"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" spans="2:11" ht="19.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="35" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="19"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
+      <c r="B36" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="19"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="19"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="B36:K38"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="A1:L2"/>
@@ -1221,50 +1271,6 @@
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="B36:K38"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
